--- a/filt-os-i18n.xlsx
+++ b/filt-os-i18n.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2886" uniqueCount="2886">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="2888">
   <si>
     <t/>
   </si>
@@ -1388,7 +1388,7 @@
     <t>trans0128</t>
   </si>
   <si>
-    <t>% 条/页</t>
+    <t>%d 条/页</t>
   </si>
   <si>
     <t>%d / page</t>
@@ -8632,6 +8632,12 @@
   </si>
   <si>
     <t>trans0961</t>
+  </si>
+  <si>
+    <t>LAN 名称</t>
+  </si>
+  <si>
+    <t>LAN Name</t>
   </si>
   <si>
     <t>trans0962</t>
@@ -12896,10 +12902,10 @@
         <v>915</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>2880</v>
+        <v>2882</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>2881</v>
+        <v>2883</v>
       </c>
       <c r="D271" s="6" t="s"/>
     </row>
@@ -14108,10 +14114,10 @@
         <v>1216</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>2882</v>
+        <v>2884</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>2883</v>
+        <v>2885</v>
       </c>
       <c r="D372" s="6" t="s"/>
     </row>
@@ -14120,10 +14126,10 @@
         <v>1217</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>2884</v>
+        <v>2886</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>2885</v>
+        <v>2887</v>
       </c>
       <c r="D373" s="6" t="s"/>
     </row>
@@ -21179,13 +21185,17 @@
       <c r="A961" s="4" t="s">
         <v>2871</v>
       </c>
-      <c r="B961" s="10" t="s"/>
-      <c r="C961" s="10" t="s"/>
+      <c r="B961" s="10" t="s">
+        <v>2872</v>
+      </c>
+      <c r="C961" s="10" t="s">
+        <v>2873</v>
+      </c>
       <c r="D961" s="6" t="s"/>
     </row>
     <row r="962" spans="1:4">
       <c r="A962" s="4" t="s">
-        <v>2872</v>
+        <v>2874</v>
       </c>
       <c r="B962" s="10" t="s"/>
       <c r="C962" s="10" t="s"/>
@@ -21193,7 +21203,7 @@
     </row>
     <row r="963" spans="1:4">
       <c r="A963" s="4" t="s">
-        <v>2873</v>
+        <v>2875</v>
       </c>
       <c r="B963" s="10" t="s"/>
       <c r="C963" s="10" t="s"/>
@@ -21201,7 +21211,7 @@
     </row>
     <row r="964" spans="1:4">
       <c r="A964" s="4" t="s">
-        <v>2874</v>
+        <v>2876</v>
       </c>
       <c r="B964" s="10" t="s"/>
       <c r="C964" s="10" t="s"/>
@@ -21209,7 +21219,7 @@
     </row>
     <row r="965" spans="1:4">
       <c r="A965" s="4" t="s">
-        <v>2875</v>
+        <v>2877</v>
       </c>
       <c r="B965" s="10" t="s"/>
       <c r="C965" s="10" t="s"/>
@@ -21217,7 +21227,7 @@
     </row>
     <row r="966" spans="1:4">
       <c r="A966" s="4" t="s">
-        <v>2876</v>
+        <v>2878</v>
       </c>
       <c r="B966" s="10" t="s"/>
       <c r="C966" s="10" t="s"/>
@@ -21225,7 +21235,7 @@
     </row>
     <row r="967" spans="1:4">
       <c r="A967" s="4" t="s">
-        <v>2877</v>
+        <v>2879</v>
       </c>
       <c r="B967" s="10" t="s"/>
       <c r="C967" s="10" t="s"/>
@@ -21233,7 +21243,7 @@
     </row>
     <row r="968" spans="1:4">
       <c r="A968" s="4" t="s">
-        <v>2878</v>
+        <v>2880</v>
       </c>
       <c r="B968" s="10" t="s"/>
       <c r="C968" s="10" t="s"/>
@@ -21241,7 +21251,7 @@
     </row>
     <row r="969" spans="1:4">
       <c r="A969" s="4" t="s">
-        <v>2879</v>
+        <v>2881</v>
       </c>
       <c r="B969" s="10" t="s"/>
       <c r="C969" s="10" t="s"/>

--- a/filt-os-i18n.xlsx
+++ b/filt-os-i18n.xlsx
@@ -327,10 +327,10 @@
     <t>trans0026</t>
   </si>
   <si>
-    <t>Mesh组网设置说明</t>
-  </si>
-  <si>
-    <t>Mesh Networking Setting Instructions</t>
+    <t>Easy Mesh 组网设置说明</t>
+  </si>
+  <si>
+    <t>Easy Mesh Networking Setting Instructions</t>
   </si>
   <si>
     <t>Instrucciones de configuración de red de malla</t>
@@ -663,7 +663,7 @@
     <t>trans0061</t>
   </si>
   <si>
-    <t>点此查看Mesh组网设置说明</t>
+    <t>点此查看 Easy Mesh 组网设置说明</t>
   </si>
   <si>
     <t>View the Mesh networking setup instructions</t>
@@ -1298,10 +1298,10 @@
     <t>trans0120</t>
   </si>
   <si>
-    <t>Mesh 拓扑图</t>
-  </si>
-  <si>
-    <t>Mesh Topology</t>
+    <t>Easy Mesh 拓扑图</t>
+  </si>
+  <si>
+    <t>Easy Mesh Topology</t>
   </si>
   <si>
     <t>Topología de malla</t>
@@ -4919,10 +4919,10 @@
     <t>trans0521</t>
   </si>
   <si>
-    <t>若要使用Mesh功能，推荐将 Wi-Fi 安全模式设置为 %s</t>
-  </si>
-  <si>
-    <t>To use the Mesh function, please set the Wi-Fi security mode to %s</t>
+    <t>若要使用 Easy Mesh 功能，推荐将 Wi-Fi 安全模式设置为 %s</t>
+  </si>
+  <si>
+    <t>To use the Easy Mesh function, please set the Wi-Fi security mode to %s</t>
   </si>
   <si>
     <t>trans0522</t>
@@ -5303,7 +5303,7 @@
     <t>路由器切换到 Bridge（AP）模式后，后续可通过访问%s页面管理本设备。同时，请确认上行路由器维护 IP 地址不是%s，避免 IP 冲突导致网络异常</t>
   </si>
   <si>
-    <t>After Mesh Router switch to bridge mode, enter the WEB through IP %s for management,the uplink router could not be %s at the same time,avoid IP conflict.</t>
+    <t>After Router switch to bridge mode, enter the WEB through IP %s for management,the uplink router could not be %s at the same time,avoid IP conflict.</t>
   </si>
   <si>
     <t>trans0565</t>
@@ -5336,10 +5336,10 @@
     <t>trans0568</t>
   </si>
   <si>
-    <t>Mesh 设置</t>
-  </si>
-  <si>
-    <t>Mesh Settings</t>
+    <t>Easy Mesh 设置</t>
+  </si>
+  <si>
+    <t>Easy Mesh Settings</t>
   </si>
   <si>
     <t>trans0569</t>
@@ -5399,10 +5399,10 @@
     <t>trans0575</t>
   </si>
   <si>
-    <t>在该页面查看Mesh状态或者修改Mesh设置。启用Mesh时，可以同时设置设备的角色，也可以在该页面触发Mesh组网过程</t>
-  </si>
-  <si>
-    <t>View Mesh Status or modify Mesh settings on this page. When Mesh is enabled, the role of the device can be set at the same time, or the Mesh network process can be triggered on this page</t>
+    <t>在该页面查看 Easy Mesh 状态或者修改 Easy Mesh 设置。启用 Easy Mesh 时，可以同时设置设备的角色，也可以在该页面触发 Easy Mesh 组网过程</t>
+  </si>
+  <si>
+    <t>View Easy Mesh Status or modify Easy Mesh settings on this page. When Easy Mesh is enabled, the role of the device can be set at the same time, or the Easy Mesh network process can be triggered on this page</t>
   </si>
   <si>
     <t>trans0576</t>
@@ -5978,7 +5978,7 @@
     <t>trans0641</t>
   </si>
   <si>
-    <t>Mesh</t>
+    <t>Easy Mesh</t>
   </si>
   <si>
     <t>trans0642</t>
@@ -8625,10 +8625,10 @@
     <t>trans0960</t>
   </si>
   <si>
-    <t>为了确保 Mesh 有效工作，请将安全模式设为 WPA2-PSK(CCMP)</t>
-  </si>
-  <si>
-    <t>To ensure the mesh function works properly, please set the security mode to WPA2-PSK with CCMP encryption.</t>
+    <t>为了确保 Easy Mesh 有效工作，请将安全模式设为 WPA2-PSK(CCMP)</t>
+  </si>
+  <si>
+    <t>To ensure the Easy Mesh function works properly, please set the security mode to WPA2-PSK with CCMP encryption.</t>
   </si>
   <si>
     <t>trans0961</t>

--- a/filt-os-i18n.xlsx
+++ b/filt-os-i18n.xlsx
@@ -666,7 +666,7 @@
     <t>点此查看 Easy Mesh 组网设置说明</t>
   </si>
   <si>
-    <t>View the Mesh networking setup instructions</t>
+    <t>View the Easy Mesh networking setup instructions</t>
   </si>
   <si>
     <t>Ver las instrucciones de configuración de red de malla</t>

--- a/filt-os-i18n.xlsx
+++ b/filt-os-i18n.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2888" uniqueCount="2888">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2889" uniqueCount="2889">
   <si>
     <t/>
   </si>
@@ -8641,6 +8641,9 @@
   </si>
   <si>
     <t>trans0962</t>
+  </si>
+  <si>
+    <t>通话中</t>
   </si>
   <si>
     <t>trans0963</t>
@@ -12902,10 +12905,10 @@
         <v>915</v>
       </c>
       <c r="B271" s="10" t="s">
-        <v>2882</v>
+        <v>2883</v>
       </c>
       <c r="C271" s="10" t="s">
-        <v>2883</v>
+        <v>2884</v>
       </c>
       <c r="D271" s="6" t="s"/>
     </row>
@@ -14114,10 +14117,10 @@
         <v>1216</v>
       </c>
       <c r="B372" s="10" t="s">
-        <v>2884</v>
+        <v>2885</v>
       </c>
       <c r="C372" s="10" t="s">
-        <v>2885</v>
+        <v>2886</v>
       </c>
       <c r="D372" s="6" t="s"/>
     </row>
@@ -14126,10 +14129,10 @@
         <v>1217</v>
       </c>
       <c r="B373" s="10" t="s">
-        <v>2886</v>
+        <v>2887</v>
       </c>
       <c r="C373" s="10" t="s">
-        <v>2887</v>
+        <v>2888</v>
       </c>
       <c r="D373" s="6" t="s"/>
     </row>
@@ -21197,13 +21200,17 @@
       <c r="A962" s="4" t="s">
         <v>2874</v>
       </c>
-      <c r="B962" s="10" t="s"/>
-      <c r="C962" s="10" t="s"/>
+      <c r="B962" s="10" t="s">
+        <v>2875</v>
+      </c>
+      <c r="C962" s="10" t="s">
+        <v>2019</v>
+      </c>
       <c r="D962" s="6" t="s"/>
     </row>
     <row r="963" spans="1:4">
       <c r="A963" s="4" t="s">
-        <v>2875</v>
+        <v>2876</v>
       </c>
       <c r="B963" s="10" t="s"/>
       <c r="C963" s="10" t="s"/>
@@ -21211,7 +21218,7 @@
     </row>
     <row r="964" spans="1:4">
       <c r="A964" s="4" t="s">
-        <v>2876</v>
+        <v>2877</v>
       </c>
       <c r="B964" s="10" t="s"/>
       <c r="C964" s="10" t="s"/>
@@ -21219,7 +21226,7 @@
     </row>
     <row r="965" spans="1:4">
       <c r="A965" s="4" t="s">
-        <v>2877</v>
+        <v>2878</v>
       </c>
       <c r="B965" s="10" t="s"/>
       <c r="C965" s="10" t="s"/>
@@ -21227,7 +21234,7 @@
     </row>
     <row r="966" spans="1:4">
       <c r="A966" s="4" t="s">
-        <v>2878</v>
+        <v>2879</v>
       </c>
       <c r="B966" s="10" t="s"/>
       <c r="C966" s="10" t="s"/>
@@ -21235,7 +21242,7 @@
     </row>
     <row r="967" spans="1:4">
       <c r="A967" s="4" t="s">
-        <v>2879</v>
+        <v>2880</v>
       </c>
       <c r="B967" s="10" t="s"/>
       <c r="C967" s="10" t="s"/>
@@ -21243,7 +21250,7 @@
     </row>
     <row r="968" spans="1:4">
       <c r="A968" s="4" t="s">
-        <v>2880</v>
+        <v>2881</v>
       </c>
       <c r="B968" s="10" t="s"/>
       <c r="C968" s="10" t="s"/>
@@ -21251,7 +21258,7 @@
     </row>
     <row r="969" spans="1:4">
       <c r="A969" s="4" t="s">
-        <v>2881</v>
+        <v>2882</v>
       </c>
       <c r="B969" s="10" t="s"/>
       <c r="C969" s="10" t="s"/>
